--- a/Phase-1-Literature-Review/Explainability/Papers/Criteria-Applied-for-Explainability.xlsx
+++ b/Phase-1-Literature-Review/Explainability/Papers/Criteria-Applied-for-Explainability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="414">
   <si>
     <t>Authors</t>
   </si>
@@ -1461,7 +1461,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1485,16 +1485,11 @@
     </font>
     <font>
       <color theme="1"/>
-      <name val="Lucida Grande"/>
+      <name val="Merriweather Sans"/>
     </font>
     <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1583,7 +1578,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1634,6 +1629,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1686,28 +1684,18 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1925,7 +1913,6 @@
     <col customWidth="1" min="1" max="1" width="41.75"/>
     <col customWidth="1" min="2" max="2" width="35.75"/>
     <col customWidth="1" min="3" max="3" width="26.13"/>
-    <col customWidth="1" min="4" max="4" width="12.63"/>
     <col customWidth="1" min="5" max="5" width="21.0"/>
     <col customWidth="1" min="6" max="6" width="9.38"/>
     <col customWidth="1" min="16" max="16" width="10.0"/>
@@ -2233,7 +2220,9 @@
       <c r="E8" s="1"/>
       <c r="F8" s="2"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -2241,7 +2230,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="5" t="str">
         <f t="shared" si="1"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O8" s="10" t="b">
         <f t="shared" si="2"/>
@@ -2269,7 +2258,7 @@
         <v>2024.0</v>
       </c>
       <c r="E9" s="15"/>
-      <c r="F9" s="19"/>
+      <c r="F9" s="20"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -2288,10 +2277,10 @@
         <v>0</v>
       </c>
       <c r="P9" s="12"/>
-      <c r="Q9" s="20" t="s">
+      <c r="Q9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="20" t="s">
+      <c r="R9" s="21" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2308,10 +2297,10 @@
       <c r="D10" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="19"/>
+      <c r="F10" s="20"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
@@ -2328,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="12"/>
-      <c r="Q10" s="21" t="s">
+      <c r="Q10" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="R10" s="21" t="s">
+      <c r="R10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2349,7 +2338,7 @@
         <v>2024.0</v>
       </c>
       <c r="E11" s="15"/>
-      <c r="F11" s="19"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
         <v>17</v>
@@ -2368,8 +2357,8 @@
         <v>1</v>
       </c>
       <c r="P11" s="12"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="15" t="s">
@@ -2378,14 +2367,14 @@
       <c r="B12" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>59</v>
       </c>
       <c r="D12" s="16">
         <v>2024.0</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="19"/>
+      <c r="F12" s="20"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -2403,9 +2392,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="25"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="26"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="15" t="s">
@@ -2421,7 +2410,7 @@
         <v>2025.0</v>
       </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="19"/>
+      <c r="F13" s="20"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
@@ -2440,12 +2429,12 @@
         <v>0</v>
       </c>
       <c r="P13" s="12"/>
-      <c r="Q13" s="26" t="s">
+      <c r="Q13" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="R13" s="27">
+      <c r="R13" s="28">
         <f>COUNTIF(N:N, "Yes")</f>
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -2461,8 +2450,8 @@
       <c r="D14" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
@@ -2495,7 +2484,7 @@
         <v>2024.0</v>
       </c>
       <c r="E15" s="15"/>
-      <c r="F15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
@@ -2527,8 +2516,8 @@
       <c r="D16" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -2560,8 +2549,8 @@
       <c r="D17" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
         <v>17</v>
@@ -2590,7 +2579,7 @@
       <c r="C18" s="15"/>
       <c r="D18" s="16"/>
       <c r="E18" s="15"/>
-      <c r="F18" s="19"/>
+      <c r="F18" s="20"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
@@ -2621,7 +2610,7 @@
       </c>
       <c r="D19" s="16"/>
       <c r="E19" s="15"/>
-      <c r="F19" s="19"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
@@ -2654,7 +2643,7 @@
         <v>2024.0</v>
       </c>
       <c r="E20" s="15"/>
-      <c r="F20" s="19"/>
+      <c r="F20" s="20"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -2683,7 +2672,7 @@
       <c r="C21" s="15"/>
       <c r="D21" s="16"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="19"/>
+      <c r="F21" s="20"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
@@ -2714,7 +2703,7 @@
         <v>2025.0</v>
       </c>
       <c r="E22" s="15"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="20"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -2746,8 +2735,8 @@
       <c r="D23" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -2782,7 +2771,7 @@
       <c r="E24" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="19"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
         <v>17</v>
@@ -2813,7 +2802,7 @@
       <c r="E25" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="19"/>
+      <c r="F25" s="20"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
@@ -2842,7 +2831,7 @@
       <c r="E26" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="19"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
@@ -2871,7 +2860,7 @@
       <c r="E27" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F27" s="19"/>
+      <c r="F27" s="20"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
@@ -2902,7 +2891,7 @@
       <c r="E28" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="19"/>
+      <c r="F28" s="20"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
         <v>17</v>
@@ -2935,7 +2924,7 @@
       <c r="E29" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="19"/>
+      <c r="F29" s="20"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
@@ -2966,7 +2955,7 @@
       <c r="E30" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="19"/>
+      <c r="F30" s="20"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
         <v>17</v>
@@ -2996,10 +2985,10 @@
       <c r="D31" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F31" s="19"/>
+      <c r="F31" s="20"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
         <v>17</v>
@@ -3029,10 +3018,10 @@
       <c r="D32" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F32" s="19"/>
+      <c r="F32" s="20"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
         <v>17</v>
@@ -3065,7 +3054,7 @@
       <c r="E33" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="19"/>
+      <c r="F33" s="20"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
         <v>17</v>
@@ -3098,7 +3087,7 @@
       <c r="E34" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F34" s="19"/>
+      <c r="F34" s="20"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
         <v>17</v>
@@ -3128,10 +3117,10 @@
       <c r="D35" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F35" s="19"/>
+      <c r="F35" s="20"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3" t="s">
         <v>17</v>
@@ -3157,14 +3146,14 @@
       <c r="B36" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="19"/>
+      <c r="C36" s="20"/>
       <c r="D36" s="16">
         <v>2024.0</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F36" s="19"/>
+      <c r="F36" s="20"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
         <v>17</v>
@@ -3197,7 +3186,7 @@
       <c r="E37" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F37" s="19"/>
+      <c r="F37" s="20"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
         <v>17</v>
@@ -3227,10 +3216,10 @@
       <c r="D38" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F38" s="19"/>
+      <c r="F38" s="20"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3" t="s">
         <v>17</v>
@@ -3263,7 +3252,7 @@
       <c r="E39" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F39" s="19"/>
+      <c r="F39" s="20"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
         <v>17</v>
@@ -3296,7 +3285,7 @@
       <c r="E40" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F40" s="19"/>
+      <c r="F40" s="20"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3" t="s">
         <v>17</v>
@@ -3322,14 +3311,14 @@
       <c r="B41" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C41" s="19"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F41" s="19"/>
+      <c r="F41" s="20"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
         <v>17</v>
@@ -3359,10 +3348,10 @@
       <c r="D42" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F42" s="19"/>
+      <c r="F42" s="20"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
         <v>17</v>
@@ -3395,7 +3384,7 @@
       <c r="E43" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F43" s="19"/>
+      <c r="F43" s="20"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
         <v>17</v>
@@ -3428,7 +3417,7 @@
       <c r="E44" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F44" s="19"/>
+      <c r="F44" s="20"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
         <v>17</v>
@@ -3461,7 +3450,7 @@
       <c r="E45" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F45" s="19"/>
+      <c r="F45" s="20"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
         <v>17</v>
@@ -3487,14 +3476,14 @@
       <c r="B46" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="19"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="16">
         <v>2024.0</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F46" s="19"/>
+      <c r="F46" s="20"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="4"/>
@@ -3518,14 +3507,14 @@
       <c r="B47" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="19"/>
+      <c r="C47" s="20"/>
       <c r="D47" s="16">
         <v>2025.0</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F47" s="19"/>
+      <c r="F47" s="20"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
         <v>17</v>
@@ -3558,7 +3547,7 @@
       <c r="E48" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F48" s="19"/>
+      <c r="F48" s="20"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="4"/>
@@ -3589,7 +3578,7 @@
       <c r="E49" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F49" s="19"/>
+      <c r="F49" s="20"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
         <v>17</v>
@@ -3615,14 +3604,14 @@
       <c r="B50" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="C50" s="19"/>
+      <c r="C50" s="20"/>
       <c r="D50" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F50" s="19"/>
+      <c r="F50" s="20"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
         <v>17</v>
@@ -3655,7 +3644,7 @@
       <c r="E51" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F51" s="19"/>
+      <c r="F51" s="20"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3" t="s">
         <v>17</v>
@@ -3688,7 +3677,7 @@
       <c r="E52" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F52" s="19"/>
+      <c r="F52" s="20"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
         <v>17</v>
@@ -3721,7 +3710,7 @@
       <c r="E53" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F53" s="19"/>
+      <c r="F53" s="20"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
         <v>17</v>
@@ -3751,10 +3740,10 @@
       <c r="D54" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E54" s="19" t="s">
+      <c r="E54" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F54" s="19"/>
+      <c r="F54" s="20"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
         <v>17</v>
@@ -3787,7 +3776,7 @@
       <c r="E55" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F55" s="19"/>
+      <c r="F55" s="20"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
         <v>17</v>
@@ -3817,10 +3806,10 @@
       <c r="D56" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E56" s="19" t="s">
+      <c r="E56" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F56" s="19"/>
+      <c r="F56" s="20"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
         <v>17</v>
@@ -3850,10 +3839,10 @@
       <c r="D57" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F57" s="19"/>
+      <c r="F57" s="20"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
         <v>17</v>
@@ -3886,7 +3875,7 @@
       <c r="E58" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F58" s="19"/>
+      <c r="F58" s="20"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
         <v>17</v>
@@ -3919,7 +3908,7 @@
       <c r="E59" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F59" s="19"/>
+      <c r="F59" s="20"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3" t="s">
         <v>17</v>
@@ -3952,7 +3941,7 @@
       <c r="E60" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F60" s="19"/>
+      <c r="F60" s="20"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3" t="s">
         <v>17</v>
@@ -3985,7 +3974,7 @@
       <c r="E61" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="19"/>
+      <c r="F61" s="20"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3" t="s">
         <v>17</v>
@@ -4018,7 +4007,7 @@
       <c r="E62" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F62" s="19"/>
+      <c r="F62" s="20"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3" t="s">
         <v>17</v>
@@ -4044,14 +4033,14 @@
       <c r="B63" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C63" s="19"/>
+      <c r="C63" s="20"/>
       <c r="D63" s="16">
         <v>2025.0</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F63" s="19"/>
+      <c r="F63" s="20"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
         <v>17</v>
@@ -4084,7 +4073,7 @@
       <c r="E64" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F64" s="19"/>
+      <c r="F64" s="20"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
         <v>17</v>
@@ -4117,7 +4106,7 @@
       <c r="E65" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F65" s="19"/>
+      <c r="F65" s="20"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
         <v>17</v>
@@ -4143,14 +4132,14 @@
       <c r="B66" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C66" s="19"/>
+      <c r="C66" s="20"/>
       <c r="D66" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E66" s="19" t="s">
+      <c r="E66" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F66" s="19"/>
+      <c r="F66" s="20"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
         <v>17</v>
@@ -4176,14 +4165,14 @@
       <c r="B67" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="19"/>
+      <c r="C67" s="20"/>
       <c r="D67" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E67" s="19" t="s">
+      <c r="E67" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F67" s="19"/>
+      <c r="F67" s="20"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
         <v>17</v>
@@ -4209,14 +4198,14 @@
       <c r="B68" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="19"/>
+      <c r="C68" s="20"/>
       <c r="D68" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E68" s="19" t="s">
+      <c r="E68" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F68" s="19"/>
+      <c r="F68" s="20"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
         <v>17</v>
@@ -4249,7 +4238,7 @@
       <c r="E69" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F69" s="19"/>
+      <c r="F69" s="20"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
         <v>17</v>
@@ -4279,10 +4268,10 @@
       <c r="D70" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E70" s="19" t="s">
+      <c r="E70" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F70" s="19"/>
+      <c r="F70" s="20"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
         <v>17</v>
@@ -4315,7 +4304,7 @@
       <c r="E71" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F71" s="19"/>
+      <c r="F71" s="20"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
         <v>17</v>
@@ -4348,7 +4337,7 @@
       <c r="E72" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F72" s="19"/>
+      <c r="F72" s="20"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3" t="s">
         <v>17</v>
@@ -4378,10 +4367,10 @@
       <c r="D73" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E73" s="19" t="s">
+      <c r="E73" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F73" s="19"/>
+      <c r="F73" s="20"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
         <v>17</v>
@@ -4411,10 +4400,10 @@
       <c r="D74" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F74" s="19"/>
+      <c r="F74" s="20"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
         <v>17</v>
@@ -4447,7 +4436,7 @@
       <c r="E75" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F75" s="19"/>
+      <c r="F75" s="20"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
         <v>17</v>
@@ -4465,9 +4454,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P75" s="28"/>
-      <c r="Q75" s="28"/>
-      <c r="R75" s="29"/>
+      <c r="P75" s="29"/>
+      <c r="Q75" s="29"/>
+      <c r="R75" s="30"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="15" t="s">
@@ -4483,7 +4472,7 @@
       <c r="E76" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F76" s="19"/>
+      <c r="F76" s="20"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
         <v>17</v>
@@ -4513,10 +4502,10 @@
       <c r="D77" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E77" s="19" t="s">
+      <c r="E77" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F77" s="19"/>
+      <c r="F77" s="20"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
         <v>17</v>
@@ -4546,10 +4535,10 @@
       <c r="D78" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E78" s="19" t="s">
+      <c r="E78" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F78" s="19"/>
+      <c r="F78" s="20"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
         <v>17</v>
@@ -4575,14 +4564,14 @@
       <c r="B79" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C79" s="19"/>
+      <c r="C79" s="20"/>
       <c r="D79" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E79" s="19" t="s">
+      <c r="E79" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F79" s="19"/>
+      <c r="F79" s="20"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3" t="s">
         <v>17</v>
@@ -4615,7 +4604,7 @@
       <c r="E80" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F80" s="19"/>
+      <c r="F80" s="20"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
         <v>17</v>
@@ -4645,10 +4634,10 @@
       <c r="D81" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E81" s="19" t="s">
+      <c r="E81" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F81" s="19"/>
+      <c r="F81" s="20"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3" t="s">
         <v>17</v>
@@ -4674,14 +4663,14 @@
       <c r="B82" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C82" s="19"/>
+      <c r="C82" s="20"/>
       <c r="D82" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F82" s="19"/>
+      <c r="F82" s="20"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
         <v>17</v>
@@ -4711,10 +4700,10 @@
       <c r="D83" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E83" s="19" t="s">
+      <c r="E83" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F83" s="19"/>
+      <c r="F83" s="20"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3" t="s">
         <v>17</v>
@@ -4740,14 +4729,14 @@
       <c r="B84" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C84" s="19"/>
+      <c r="C84" s="20"/>
       <c r="D84" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E84" s="19" t="s">
+      <c r="E84" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F84" s="19"/>
+      <c r="F84" s="20"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3" t="s">
         <v>17</v>
@@ -4773,14 +4762,14 @@
       <c r="B85" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C85" s="19"/>
+      <c r="C85" s="20"/>
       <c r="D85" s="16">
         <v>2024.0</v>
       </c>
       <c r="E85" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F85" s="19"/>
+      <c r="F85" s="20"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3" t="s">
         <v>17</v>
@@ -4810,10 +4799,10 @@
       <c r="D86" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E86" s="19" t="s">
+      <c r="E86" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F86" s="19"/>
+      <c r="F86" s="20"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3" t="s">
         <v>17</v>
@@ -4843,10 +4832,10 @@
       <c r="D87" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E87" s="19" t="s">
+      <c r="E87" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F87" s="19"/>
+      <c r="F87" s="20"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3" t="s">
         <v>17</v>
@@ -4872,14 +4861,14 @@
       <c r="B88" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="C88" s="19"/>
+      <c r="C88" s="20"/>
       <c r="D88" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E88" s="19" t="s">
+      <c r="E88" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F88" s="19"/>
+      <c r="F88" s="20"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3" t="s">
         <v>17</v>
@@ -4912,7 +4901,7 @@
       <c r="E89" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F89" s="19"/>
+      <c r="F89" s="20"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
       <c r="I89" s="4"/>
@@ -4940,10 +4929,10 @@
       <c r="D90" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E90" s="19" t="s">
+      <c r="E90" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F90" s="19"/>
+      <c r="F90" s="20"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="4"/>
@@ -4973,10 +4962,10 @@
       <c r="D91" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E91" s="19" t="s">
+      <c r="E91" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F91" s="19"/>
+      <c r="F91" s="20"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3" t="s">
         <v>17</v>
@@ -5009,7 +4998,7 @@
       <c r="E92" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F92" s="19"/>
+      <c r="F92" s="20"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3" t="s">
         <v>17</v>
@@ -5039,10 +5028,10 @@
       <c r="D93" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E93" s="19" t="s">
+      <c r="E93" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F93" s="19"/>
+      <c r="F93" s="20"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3" t="s">
         <v>17</v>
@@ -5072,10 +5061,10 @@
       <c r="D94" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E94" s="19" t="s">
+      <c r="E94" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F94" s="19"/>
+      <c r="F94" s="20"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3" t="s">
         <v>17</v>
@@ -5108,7 +5097,7 @@
       <c r="E95" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F95" s="19"/>
+      <c r="F95" s="20"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3" t="s">
         <v>17</v>
@@ -5141,7 +5130,7 @@
       <c r="E96" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F96" s="19"/>
+      <c r="F96" s="20"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
         <v>17</v>
@@ -5174,7 +5163,7 @@
       <c r="E97" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F97" s="19"/>
+      <c r="F97" s="20"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3" t="s">
         <v>17</v>
@@ -5207,7 +5196,7 @@
       <c r="E98" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F98" s="19"/>
+      <c r="F98" s="20"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3" t="s">
         <v>17</v>
@@ -5240,7 +5229,7 @@
       <c r="E99" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F99" s="19"/>
+      <c r="F99" s="20"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3" t="s">
         <v>17</v>
@@ -5273,7 +5262,7 @@
       <c r="E100" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F100" s="19"/>
+      <c r="F100" s="20"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3" t="s">
         <v>17</v>
@@ -5306,7 +5295,7 @@
       <c r="E101" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F101" s="19"/>
+      <c r="F101" s="20"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
         <v>17</v>
@@ -5336,10 +5325,10 @@
       <c r="D102" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E102" s="19" t="s">
+      <c r="E102" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F102" s="19"/>
+      <c r="F102" s="20"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3" t="s">
         <v>17</v>
@@ -5372,7 +5361,7 @@
       <c r="E103" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F103" s="19"/>
+      <c r="F103" s="20"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3" t="s">
         <v>17</v>
@@ -5405,7 +5394,7 @@
       <c r="E104" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F104" s="19"/>
+      <c r="F104" s="20"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3" t="s">
         <v>17</v>
@@ -5438,7 +5427,7 @@
       <c r="E105" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F105" s="19"/>
+      <c r="F105" s="20"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
       <c r="I105" s="4"/>
@@ -5469,7 +5458,7 @@
       <c r="E106" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F106" s="19"/>
+      <c r="F106" s="20"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3" t="s">
         <v>17</v>
@@ -5495,14 +5484,14 @@
       <c r="B107" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C107" s="19"/>
+      <c r="C107" s="20"/>
       <c r="D107" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E107" s="19" t="s">
+      <c r="E107" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F107" s="19"/>
+      <c r="F107" s="20"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3" t="s">
         <v>17</v>
@@ -5535,7 +5524,7 @@
       <c r="E108" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F108" s="19"/>
+      <c r="F108" s="20"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
         <v>17</v>
@@ -5568,7 +5557,7 @@
       <c r="E109" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F109" s="19"/>
+      <c r="F109" s="20"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3" t="s">
         <v>17</v>
@@ -5594,14 +5583,14 @@
       <c r="B110" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C110" s="19"/>
+      <c r="C110" s="20"/>
       <c r="D110" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E110" s="19" t="s">
+      <c r="E110" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F110" s="19"/>
+      <c r="F110" s="20"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3" t="s">
         <v>17</v>
@@ -5634,7 +5623,7 @@
       <c r="E111" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F111" s="19"/>
+      <c r="F111" s="20"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3" t="s">
         <v>17</v>
@@ -5664,10 +5653,10 @@
       <c r="D112" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E112" s="19" t="s">
+      <c r="E112" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F112" s="19"/>
+      <c r="F112" s="20"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3" t="s">
         <v>17</v>
@@ -5700,7 +5689,7 @@
       <c r="E113" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F113" s="19"/>
+      <c r="F113" s="20"/>
       <c r="G113" s="3"/>
       <c r="H113" s="3" t="s">
         <v>17</v>
@@ -5730,10 +5719,10 @@
       <c r="D114" s="16">
         <v>2023.0</v>
       </c>
-      <c r="E114" s="19" t="s">
+      <c r="E114" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F114" s="19"/>
+      <c r="F114" s="20"/>
       <c r="G114" s="3"/>
       <c r="H114" s="3" t="s">
         <v>17</v>
@@ -5766,7 +5755,7 @@
       <c r="E115" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F115" s="19"/>
+      <c r="F115" s="20"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3" t="s">
         <v>17</v>
@@ -5796,10 +5785,10 @@
       <c r="D116" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E116" s="19" t="s">
+      <c r="E116" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F116" s="19"/>
+      <c r="F116" s="20"/>
       <c r="G116" s="3"/>
       <c r="H116" s="3" t="s">
         <v>17</v>
@@ -5832,7 +5821,7 @@
       <c r="E117" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F117" s="19"/>
+      <c r="F117" s="20"/>
       <c r="G117" s="3"/>
       <c r="H117" s="3" t="s">
         <v>17</v>
@@ -5865,7 +5854,7 @@
       <c r="E118" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F118" s="19"/>
+      <c r="F118" s="20"/>
       <c r="G118" s="3"/>
       <c r="H118" s="3" t="s">
         <v>17</v>
@@ -5898,7 +5887,7 @@
       <c r="E119" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F119" s="19"/>
+      <c r="F119" s="20"/>
       <c r="G119" s="3"/>
       <c r="H119" s="3" t="s">
         <v>17</v>
@@ -5928,10 +5917,10 @@
       <c r="D120" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E120" s="19" t="s">
+      <c r="E120" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F120" s="19"/>
+      <c r="F120" s="20"/>
       <c r="G120" s="3"/>
       <c r="H120" s="3" t="s">
         <v>17</v>
@@ -5964,7 +5953,7 @@
       <c r="E121" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F121" s="19"/>
+      <c r="F121" s="20"/>
       <c r="G121" s="3"/>
       <c r="H121" s="3" t="s">
         <v>17</v>
@@ -5997,7 +5986,7 @@
       <c r="E122" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F122" s="19"/>
+      <c r="F122" s="20"/>
       <c r="G122" s="3"/>
       <c r="H122" s="3" t="s">
         <v>17</v>
@@ -6030,7 +6019,7 @@
       <c r="E123" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F123" s="19"/>
+      <c r="F123" s="20"/>
       <c r="G123" s="3"/>
       <c r="H123" s="3" t="s">
         <v>17</v>
@@ -6060,10 +6049,10 @@
       <c r="D124" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E124" s="19" t="s">
+      <c r="E124" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F124" s="19"/>
+      <c r="F124" s="20"/>
       <c r="G124" s="3"/>
       <c r="H124" s="3" t="s">
         <v>17</v>
@@ -6093,10 +6082,10 @@
       <c r="D125" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E125" s="19" t="s">
+      <c r="E125" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F125" s="19"/>
+      <c r="F125" s="20"/>
       <c r="G125" s="3"/>
       <c r="H125" s="3" t="s">
         <v>17</v>
@@ -6126,10 +6115,10 @@
       <c r="D126" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E126" s="19" t="s">
+      <c r="E126" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F126" s="19"/>
+      <c r="F126" s="20"/>
       <c r="G126" s="3"/>
       <c r="H126" s="3"/>
       <c r="I126" s="4"/>
@@ -6160,7 +6149,7 @@
       <c r="E127" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F127" s="19"/>
+      <c r="F127" s="20"/>
       <c r="G127" s="3"/>
       <c r="H127" s="3"/>
       <c r="I127" s="4" t="s">
@@ -6193,7 +6182,7 @@
       <c r="E128" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F128" s="19"/>
+      <c r="F128" s="20"/>
       <c r="G128" s="3"/>
       <c r="H128" s="3"/>
       <c r="I128" s="4"/>
@@ -6224,7 +6213,7 @@
       <c r="E129" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F129" s="19"/>
+      <c r="F129" s="20"/>
       <c r="G129" s="3"/>
       <c r="H129" s="3" t="s">
         <v>17</v>
@@ -6257,7 +6246,7 @@
       <c r="E130" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F130" s="19"/>
+      <c r="F130" s="20"/>
       <c r="G130" s="3"/>
       <c r="H130" s="3" t="s">
         <v>17</v>
@@ -6290,7 +6279,7 @@
       <c r="E131" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F131" s="19"/>
+      <c r="F131" s="20"/>
       <c r="G131" s="3"/>
       <c r="H131" s="3" t="s">
         <v>17</v>
@@ -6323,7 +6312,7 @@
       <c r="E132" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F132" s="19"/>
+      <c r="F132" s="20"/>
       <c r="G132" s="3"/>
       <c r="H132" s="3" t="s">
         <v>17</v>
@@ -6356,7 +6345,7 @@
       <c r="E133" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F133" s="19"/>
+      <c r="F133" s="20"/>
       <c r="G133" s="3"/>
       <c r="H133" s="3" t="s">
         <v>17</v>
@@ -6389,7 +6378,7 @@
       <c r="E134" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F134" s="19"/>
+      <c r="F134" s="20"/>
       <c r="G134" s="3"/>
       <c r="H134" s="3" t="s">
         <v>17</v>
@@ -6422,7 +6411,7 @@
       <c r="E135" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F135" s="19"/>
+      <c r="F135" s="20"/>
       <c r="G135" s="3"/>
       <c r="H135" s="3" t="s">
         <v>17</v>
@@ -6448,14 +6437,14 @@
       <c r="B136" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="C136" s="19"/>
+      <c r="C136" s="20"/>
       <c r="D136" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E136" s="19" t="s">
+      <c r="E136" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F136" s="19"/>
+      <c r="F136" s="20"/>
       <c r="G136" s="3"/>
       <c r="H136" s="3" t="s">
         <v>17</v>
@@ -6485,10 +6474,10 @@
       <c r="D137" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E137" s="19" t="s">
+      <c r="E137" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F137" s="19"/>
+      <c r="F137" s="20"/>
       <c r="G137" s="3"/>
       <c r="H137" s="3" t="s">
         <v>17</v>
@@ -6521,7 +6510,7 @@
       <c r="E138" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F138" s="19"/>
+      <c r="F138" s="20"/>
       <c r="G138" s="3"/>
       <c r="H138" s="3" t="s">
         <v>17</v>
@@ -6547,14 +6536,14 @@
       <c r="B139" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="C139" s="19"/>
+      <c r="C139" s="20"/>
       <c r="D139" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E139" s="19" t="s">
+      <c r="E139" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F139" s="19"/>
+      <c r="F139" s="20"/>
       <c r="G139" s="3"/>
       <c r="H139" s="3" t="s">
         <v>17</v>
@@ -6587,7 +6576,7 @@
       <c r="E140" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F140" s="19"/>
+      <c r="F140" s="20"/>
       <c r="G140" s="3"/>
       <c r="H140" s="3" t="s">
         <v>17</v>
@@ -6620,7 +6609,7 @@
       <c r="E141" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F141" s="19"/>
+      <c r="F141" s="20"/>
       <c r="G141" s="3"/>
       <c r="H141" s="3" t="s">
         <v>17</v>
@@ -6650,10 +6639,10 @@
       <c r="D142" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E142" s="19" t="s">
+      <c r="E142" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F142" s="19"/>
+      <c r="F142" s="20"/>
       <c r="G142" s="3"/>
       <c r="H142" s="3" t="s">
         <v>17</v>
@@ -6686,7 +6675,7 @@
       <c r="E143" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F143" s="19"/>
+      <c r="F143" s="20"/>
       <c r="G143" s="3"/>
       <c r="H143" s="3" t="s">
         <v>17</v>
@@ -6716,10 +6705,10 @@
       <c r="D144" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E144" s="19" t="s">
+      <c r="E144" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F144" s="19"/>
+      <c r="F144" s="20"/>
       <c r="G144" s="3"/>
       <c r="H144" s="3" t="s">
         <v>17</v>
@@ -6749,10 +6738,10 @@
       <c r="D145" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E145" s="19" t="s">
+      <c r="E145" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F145" s="19"/>
+      <c r="F145" s="20"/>
       <c r="G145" s="3"/>
       <c r="H145" s="3" t="s">
         <v>17</v>
@@ -6782,10 +6771,10 @@
       <c r="D146" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E146" s="19" t="s">
+      <c r="E146" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F146" s="19"/>
+      <c r="F146" s="20"/>
       <c r="G146" s="3"/>
       <c r="H146" s="3" t="s">
         <v>17</v>
@@ -6818,7 +6807,7 @@
       <c r="E147" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F147" s="19"/>
+      <c r="F147" s="20"/>
       <c r="G147" s="3"/>
       <c r="H147" s="3" t="s">
         <v>17</v>
@@ -6851,7 +6840,7 @@
       <c r="E148" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F148" s="19"/>
+      <c r="F148" s="20"/>
       <c r="G148" s="3"/>
       <c r="H148" s="3" t="s">
         <v>17</v>
@@ -6884,7 +6873,7 @@
       <c r="E149" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F149" s="19"/>
+      <c r="F149" s="20"/>
       <c r="G149" s="3"/>
       <c r="H149" s="3" t="s">
         <v>17</v>
@@ -6917,7 +6906,7 @@
       <c r="E150" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F150" s="19"/>
+      <c r="F150" s="20"/>
       <c r="G150" s="3"/>
       <c r="H150" s="3" t="s">
         <v>17</v>
@@ -6947,10 +6936,10 @@
       <c r="D151" s="16">
         <v>2025.0</v>
       </c>
-      <c r="E151" s="19" t="s">
+      <c r="E151" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F151" s="19"/>
+      <c r="F151" s="20"/>
       <c r="G151" s="3"/>
       <c r="H151" s="3" t="s">
         <v>17</v>
@@ -6976,14 +6965,14 @@
       <c r="B152" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="C152" s="19"/>
+      <c r="C152" s="20"/>
       <c r="D152" s="16">
         <v>2024.0</v>
       </c>
       <c r="E152" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F152" s="19"/>
+      <c r="F152" s="20"/>
       <c r="G152" s="3"/>
       <c r="H152" s="3" t="s">
         <v>17</v>
@@ -7013,10 +7002,10 @@
       <c r="D153" s="16">
         <v>2024.0</v>
       </c>
-      <c r="E153" s="19" t="s">
+      <c r="E153" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F153" s="19"/>
+      <c r="F153" s="20"/>
       <c r="G153" s="3"/>
       <c r="H153" s="3" t="s">
         <v>17</v>
@@ -7168,28 +7157,28 @@
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="30" t="s">
+      <c r="A158" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="B158" s="30" t="s">
+      <c r="B158" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C158" s="30"/>
-      <c r="D158" s="30">
+      <c r="C158" s="31"/>
+      <c r="D158" s="31">
         <v>2025.0</v>
       </c>
-      <c r="E158" s="30" t="s">
+      <c r="E158" s="31" t="s">
         <v>362</v>
       </c>
       <c r="F158" s="10"/>
-      <c r="G158" s="31"/>
-      <c r="H158" s="31"/>
-      <c r="I158" s="31"/>
-      <c r="J158" s="31"/>
-      <c r="K158" s="31"/>
-      <c r="L158" s="31"/>
-      <c r="M158" s="31"/>
-      <c r="N158" s="31" t="s">
+      <c r="G158" s="32"/>
+      <c r="H158" s="32"/>
+      <c r="I158" s="32"/>
+      <c r="J158" s="32"/>
+      <c r="K158" s="32"/>
+      <c r="L158" s="32"/>
+      <c r="M158" s="32"/>
+      <c r="N158" s="32" t="s">
         <v>364</v>
       </c>
       <c r="O158" s="10" t="b">
@@ -7240,7 +7229,9 @@
       <c r="E160" s="1"/>
       <c r="F160" s="2"/>
       <c r="G160" s="3"/>
-      <c r="H160" s="3"/>
+      <c r="H160" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="I160" s="4"/>
       <c r="J160" s="4"/>
       <c r="K160" s="4"/>
@@ -7248,7 +7239,7 @@
       <c r="M160" s="4"/>
       <c r="N160" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O160" s="10" t="b">
         <f t="shared" si="2"/>
@@ -7256,22 +7247,22 @@
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="32" t="s">
+      <c r="A161" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="B161" s="33" t="s">
+      <c r="B161" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="C161" s="34"/>
-      <c r="D161" s="35">
+      <c r="C161" s="35"/>
+      <c r="D161" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E161" s="36" t="s">
+      <c r="E161" s="35" t="s">
         <v>371</v>
       </c>
       <c r="F161" s="2"/>
       <c r="G161" s="3"/>
-      <c r="H161" s="37" t="s">
+      <c r="H161" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I161" s="4"/>
@@ -7289,19 +7280,19 @@
       </c>
     </row>
     <row r="162" ht="28.5" customHeight="1">
-      <c r="A162" s="34" t="s">
+      <c r="A162" s="35" t="s">
         <v>372</v>
       </c>
-      <c r="B162" s="38" t="s">
+      <c r="B162" s="37" t="s">
         <v>373</v>
       </c>
-      <c r="C162" s="34"/>
-      <c r="D162" s="35">
+      <c r="C162" s="35"/>
+      <c r="D162" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E162" s="34"/>
+      <c r="E162" s="35"/>
       <c r="F162" s="2"/>
-      <c r="G162" s="37" t="s">
+      <c r="G162" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H162" s="3"/>
@@ -7320,28 +7311,32 @@
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="34" t="s">
+      <c r="A163" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="B163" s="38" t="s">
+      <c r="B163" s="37" t="s">
         <v>375</v>
       </c>
-      <c r="C163" s="34"/>
-      <c r="D163" s="35">
+      <c r="C163" s="35"/>
+      <c r="D163" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E163" s="34"/>
+      <c r="E163" s="35"/>
       <c r="F163" s="2"/>
       <c r="G163" s="3"/>
-      <c r="H163" s="3"/>
+      <c r="H163" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="I163" s="4"/>
-      <c r="J163" s="4"/>
+      <c r="J163" s="38" t="s">
+        <v>17</v>
+      </c>
       <c r="K163" s="4"/>
       <c r="L163" s="4"/>
       <c r="M163" s="4"/>
       <c r="N163" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O163" s="10" t="b">
         <f t="shared" si="2"/>
@@ -7349,22 +7344,22 @@
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="39" t="s">
+      <c r="A164" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="B164" s="38" t="s">
+      <c r="B164" s="37" t="s">
         <v>377</v>
       </c>
-      <c r="C164" s="34"/>
-      <c r="D164" s="35">
+      <c r="C164" s="35"/>
+      <c r="D164" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E164" s="34"/>
+      <c r="E164" s="35"/>
       <c r="F164" s="2"/>
-      <c r="G164" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="H164" s="37"/>
+      <c r="G164" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H164" s="3"/>
       <c r="I164" s="4"/>
       <c r="J164" s="4"/>
       <c r="K164" s="4"/>
@@ -7380,20 +7375,22 @@
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="34" t="s">
+      <c r="A165" s="35" t="s">
         <v>378</v>
       </c>
-      <c r="B165" s="38" t="s">
+      <c r="B165" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="C165" s="34"/>
-      <c r="D165" s="35">
+      <c r="C165" s="35"/>
+      <c r="D165" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E165" s="34"/>
+      <c r="E165" s="35"/>
       <c r="F165" s="2"/>
       <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
+      <c r="H165" s="19" t="s">
+        <v>17</v>
+      </c>
       <c r="I165" s="4"/>
       <c r="J165" s="4"/>
       <c r="K165" s="4"/>
@@ -7401,7 +7398,7 @@
       <c r="M165" s="4"/>
       <c r="N165" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O165" s="10" t="b">
         <f t="shared" si="2"/>
@@ -7409,26 +7406,28 @@
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="34" t="s">
+      <c r="A166" s="35" t="s">
         <v>380</v>
       </c>
-      <c r="B166" s="38" t="s">
+      <c r="B166" s="37" t="s">
         <v>381</v>
       </c>
-      <c r="C166" s="34"/>
-      <c r="D166" s="34"/>
-      <c r="E166" s="34"/>
+      <c r="C166" s="35"/>
+      <c r="D166" s="35"/>
+      <c r="E166" s="35"/>
       <c r="F166" s="2"/>
       <c r="G166" s="3"/>
-      <c r="H166" s="3"/>
-      <c r="I166" s="4"/>
+      <c r="H166" s="19"/>
+      <c r="I166" s="38" t="s">
+        <v>17</v>
+      </c>
       <c r="J166" s="4"/>
       <c r="K166" s="4"/>
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
       <c r="N166" s="5" t="str">
         <f t="shared" si="3"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O166" s="10" t="b">
         <f t="shared" si="2"/>
@@ -7436,22 +7435,22 @@
       </c>
     </row>
     <row r="167" ht="37.5" customHeight="1">
-      <c r="A167" s="34" t="s">
+      <c r="A167" s="35" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="40" t="s">
+      <c r="B167" s="39" t="s">
         <v>383</v>
       </c>
-      <c r="C167" s="34"/>
-      <c r="D167" s="35">
+      <c r="C167" s="35"/>
+      <c r="D167" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E167" s="34" t="s">
+      <c r="E167" s="35" t="s">
         <v>362</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" s="3"/>
-      <c r="H167" s="37" t="s">
+      <c r="H167" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I167" s="4"/>
@@ -7469,17 +7468,17 @@
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="34" t="s">
+      <c r="A168" s="35" t="s">
         <v>384</v>
       </c>
-      <c r="B168" s="40" t="s">
+      <c r="B168" s="39" t="s">
         <v>385</v>
       </c>
-      <c r="C168" s="34"/>
-      <c r="D168" s="35">
+      <c r="C168" s="35"/>
+      <c r="D168" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E168" s="34" t="s">
+      <c r="E168" s="35" t="s">
         <v>35</v>
       </c>
       <c r="F168" s="2"/>
@@ -7500,19 +7499,19 @@
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="34" t="s">
+      <c r="A169" s="35" t="s">
         <v>386</v>
       </c>
-      <c r="B169" s="40" t="s">
+      <c r="B169" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="C169" s="34"/>
-      <c r="D169" s="35">
+      <c r="C169" s="35"/>
+      <c r="D169" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E169" s="34"/>
+      <c r="E169" s="35"/>
       <c r="F169" s="2"/>
-      <c r="G169" s="37" t="s">
+      <c r="G169" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H169" s="3"/>
@@ -7531,17 +7530,17 @@
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="34" t="s">
+      <c r="A170" s="35" t="s">
         <v>388</v>
       </c>
-      <c r="B170" s="40" t="s">
+      <c r="B170" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="34"/>
-      <c r="D170" s="35">
+      <c r="C170" s="35"/>
+      <c r="D170" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E170" s="34" t="s">
+      <c r="E170" s="35" t="s">
         <v>390</v>
       </c>
       <c r="F170" s="2"/>
@@ -7562,17 +7561,17 @@
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="34" t="s">
+      <c r="A171" s="35" t="s">
         <v>391</v>
       </c>
-      <c r="B171" s="40" t="s">
+      <c r="B171" s="39" t="s">
         <v>392</v>
       </c>
-      <c r="C171" s="34"/>
-      <c r="D171" s="35">
+      <c r="C171" s="35"/>
+      <c r="D171" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E171" s="34" t="s">
+      <c r="E171" s="35" t="s">
         <v>393</v>
       </c>
       <c r="F171" s="2"/>
@@ -7593,17 +7592,17 @@
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="34" t="s">
+      <c r="A172" s="35" t="s">
         <v>394</v>
       </c>
-      <c r="B172" s="40" t="s">
+      <c r="B172" s="39" t="s">
         <v>395</v>
       </c>
-      <c r="C172" s="34"/>
-      <c r="D172" s="35">
+      <c r="C172" s="35"/>
+      <c r="D172" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E172" s="34" t="s">
+      <c r="E172" s="35" t="s">
         <v>396</v>
       </c>
       <c r="F172" s="2"/>
@@ -7624,19 +7623,19 @@
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="39" t="s">
+      <c r="A173" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="B173" s="38" t="s">
+      <c r="B173" s="37" t="s">
         <v>398</v>
       </c>
-      <c r="C173" s="34"/>
-      <c r="D173" s="35">
+      <c r="C173" s="35"/>
+      <c r="D173" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E173" s="34"/>
+      <c r="E173" s="35"/>
       <c r="F173" s="2"/>
-      <c r="G173" s="37" t="s">
+      <c r="G173" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H173" s="3"/>
@@ -7655,19 +7654,19 @@
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="33" t="s">
+      <c r="A174" s="34" t="s">
         <v>399</v>
       </c>
-      <c r="B174" s="38" t="s">
+      <c r="B174" s="37" t="s">
         <v>400</v>
       </c>
-      <c r="C174" s="34"/>
-      <c r="D174" s="35">
+      <c r="C174" s="35"/>
+      <c r="D174" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E174" s="34"/>
+      <c r="E174" s="35"/>
       <c r="F174" s="2"/>
-      <c r="G174" s="37" t="s">
+      <c r="G174" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H174" s="3"/>
@@ -7686,22 +7685,22 @@
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="34" t="s">
+      <c r="A175" s="35" t="s">
         <v>401</v>
       </c>
-      <c r="B175" s="40" t="s">
+      <c r="B175" s="39" t="s">
         <v>402</v>
       </c>
-      <c r="C175" s="34"/>
-      <c r="D175" s="35">
+      <c r="C175" s="35"/>
+      <c r="D175" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E175" s="34" t="s">
+      <c r="E175" s="35" t="s">
         <v>35</v>
       </c>
       <c r="F175" s="2"/>
       <c r="G175" s="3"/>
-      <c r="H175" s="37" t="s">
+      <c r="H175" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I175" s="4"/>
@@ -7719,23 +7718,23 @@
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="34" t="s">
+      <c r="A176" s="35" t="s">
         <v>403</v>
       </c>
-      <c r="B176" s="40" t="s">
+      <c r="B176" s="39" t="s">
         <v>404</v>
       </c>
-      <c r="C176" s="34"/>
-      <c r="D176" s="35">
+      <c r="C176" s="35"/>
+      <c r="D176" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E176" s="34"/>
+      <c r="E176" s="35"/>
       <c r="F176" s="2"/>
       <c r="G176" s="3"/>
       <c r="H176" s="3"/>
       <c r="I176" s="4"/>
       <c r="J176" s="4"/>
-      <c r="K176" s="41" t="s">
+      <c r="K176" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L176" s="4"/>
@@ -7750,17 +7749,17 @@
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="34" t="s">
+      <c r="A177" s="35" t="s">
         <v>405</v>
       </c>
-      <c r="B177" s="40" t="s">
+      <c r="B177" s="39" t="s">
         <v>406</v>
       </c>
-      <c r="C177" s="34"/>
-      <c r="D177" s="35">
+      <c r="C177" s="35"/>
+      <c r="D177" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E177" s="34"/>
+      <c r="E177" s="35"/>
       <c r="F177" s="2"/>
       <c r="G177" s="3"/>
       <c r="H177" s="3"/>
@@ -7779,17 +7778,17 @@
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="34" t="s">
+      <c r="A178" s="35" t="s">
         <v>407</v>
       </c>
-      <c r="B178" s="40" t="s">
+      <c r="B178" s="39" t="s">
         <v>408</v>
       </c>
-      <c r="C178" s="34"/>
-      <c r="D178" s="35">
+      <c r="C178" s="35"/>
+      <c r="D178" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E178" s="36" t="s">
+      <c r="E178" s="35" t="s">
         <v>409</v>
       </c>
       <c r="F178" s="2"/>
@@ -7810,19 +7809,19 @@
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="34" t="s">
+      <c r="A179" s="35" t="s">
         <v>410</v>
       </c>
-      <c r="B179" s="40" t="s">
+      <c r="B179" s="39" t="s">
         <v>411</v>
       </c>
-      <c r="C179" s="34"/>
-      <c r="D179" s="35">
+      <c r="C179" s="35"/>
+      <c r="D179" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E179" s="34"/>
+      <c r="E179" s="35"/>
       <c r="F179" s="2"/>
-      <c r="G179" s="37" t="s">
+      <c r="G179" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H179" s="3"/>
@@ -7841,19 +7840,19 @@
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="34" t="s">
+      <c r="A180" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="B180" s="40" t="s">
+      <c r="B180" s="39" t="s">
         <v>413</v>
       </c>
-      <c r="C180" s="34"/>
-      <c r="D180" s="35">
+      <c r="C180" s="35"/>
+      <c r="D180" s="36">
         <v>2025.0</v>
       </c>
-      <c r="E180" s="34"/>
+      <c r="E180" s="35"/>
       <c r="F180" s="2"/>
-      <c r="G180" s="37" t="s">
+      <c r="G180" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H180" s="3"/>
@@ -7873,7 +7872,7 @@
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="1"/>
-      <c r="B181" s="42"/>
+      <c r="B181" s="40"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -7890,7 +7889,7 @@
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="1"/>
-      <c r="B182" s="42"/>
+      <c r="B182" s="40"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -7907,7 +7906,7 @@
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1"/>
-      <c r="B183" s="42"/>
+      <c r="B183" s="40"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -7924,7 +7923,7 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1"/>
-      <c r="B184" s="42"/>
+      <c r="B184" s="40"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -7941,7 +7940,7 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1"/>
-      <c r="B185" s="42"/>
+      <c r="B185" s="40"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -7958,7 +7957,7 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1"/>
-      <c r="B186" s="42"/>
+      <c r="B186" s="40"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -7975,7 +7974,7 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1"/>
-      <c r="B187" s="42"/>
+      <c r="B187" s="40"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -7992,7 +7991,7 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1"/>
-      <c r="B188" s="42"/>
+      <c r="B188" s="40"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -8009,7 +8008,7 @@
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1"/>
-      <c r="B189" s="42"/>
+      <c r="B189" s="40"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -8026,7 +8025,7 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1"/>
-      <c r="B190" s="42"/>
+      <c r="B190" s="40"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -8043,7 +8042,7 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1"/>
-      <c r="B191" s="42"/>
+      <c r="B191" s="40"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -8060,7 +8059,7 @@
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1"/>
-      <c r="B192" s="42"/>
+      <c r="B192" s="40"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -8077,7 +8076,7 @@
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1"/>
-      <c r="B193" s="42"/>
+      <c r="B193" s="40"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -8094,7 +8093,7 @@
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1"/>
-      <c r="B194" s="42"/>
+      <c r="B194" s="40"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -8111,7 +8110,7 @@
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1"/>
-      <c r="B195" s="42"/>
+      <c r="B195" s="40"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -8128,7 +8127,7 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1"/>
-      <c r="B196" s="42"/>
+      <c r="B196" s="40"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -8145,7 +8144,7 @@
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1"/>
-      <c r="B197" s="42"/>
+      <c r="B197" s="40"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -10932,1924 +10931,1924 @@
       <c r="O360" s="10"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="O361" s="43"/>
+      <c r="O361" s="2"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="O362" s="43"/>
+      <c r="O362" s="2"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="O363" s="43"/>
+      <c r="O363" s="2"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="O364" s="43"/>
+      <c r="O364" s="2"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="O365" s="43"/>
+      <c r="O365" s="2"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="O366" s="43"/>
+      <c r="O366" s="2"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="O367" s="43"/>
+      <c r="O367" s="2"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="O368" s="43"/>
+      <c r="O368" s="2"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="O369" s="43"/>
+      <c r="O369" s="2"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="O370" s="43"/>
+      <c r="O370" s="2"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="O371" s="43"/>
+      <c r="O371" s="2"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="O372" s="43"/>
+      <c r="O372" s="2"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="O373" s="43"/>
+      <c r="O373" s="2"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="O374" s="43"/>
+      <c r="O374" s="2"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="O375" s="43"/>
+      <c r="O375" s="2"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="O376" s="43"/>
+      <c r="O376" s="2"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="O377" s="43"/>
+      <c r="O377" s="2"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="O378" s="43"/>
+      <c r="O378" s="2"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="O379" s="43"/>
+      <c r="O379" s="2"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="O380" s="43"/>
+      <c r="O380" s="2"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="O381" s="43"/>
+      <c r="O381" s="2"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="O382" s="43"/>
+      <c r="O382" s="2"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="O383" s="43"/>
+      <c r="O383" s="2"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="O384" s="43"/>
+      <c r="O384" s="2"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="O385" s="43"/>
+      <c r="O385" s="2"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="O386" s="43"/>
+      <c r="O386" s="2"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="O387" s="43"/>
+      <c r="O387" s="2"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="O388" s="43"/>
+      <c r="O388" s="2"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="O389" s="43"/>
+      <c r="O389" s="2"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="O390" s="43"/>
+      <c r="O390" s="2"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="O391" s="43"/>
+      <c r="O391" s="2"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="O392" s="43"/>
+      <c r="O392" s="2"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="O393" s="43"/>
+      <c r="O393" s="2"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="O394" s="43"/>
+      <c r="O394" s="2"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="O395" s="43"/>
+      <c r="O395" s="2"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="O396" s="43"/>
+      <c r="O396" s="2"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="O397" s="43"/>
+      <c r="O397" s="2"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="O398" s="43"/>
+      <c r="O398" s="2"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="O399" s="43"/>
+      <c r="O399" s="2"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="O400" s="43"/>
+      <c r="O400" s="2"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="O401" s="43"/>
+      <c r="O401" s="2"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="O402" s="43"/>
+      <c r="O402" s="2"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="O403" s="43"/>
+      <c r="O403" s="2"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="O404" s="43"/>
+      <c r="O404" s="2"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="O405" s="43"/>
+      <c r="O405" s="2"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="O406" s="43"/>
+      <c r="O406" s="2"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="O407" s="43"/>
+      <c r="O407" s="2"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="O408" s="43"/>
+      <c r="O408" s="2"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="O409" s="43"/>
+      <c r="O409" s="2"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="O410" s="43"/>
+      <c r="O410" s="2"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="O411" s="43"/>
+      <c r="O411" s="2"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="O412" s="43"/>
+      <c r="O412" s="2"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="O413" s="43"/>
+      <c r="O413" s="2"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="O414" s="43"/>
+      <c r="O414" s="2"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="O415" s="43"/>
+      <c r="O415" s="2"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="O416" s="43"/>
+      <c r="O416" s="2"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="O417" s="43"/>
+      <c r="O417" s="2"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="O418" s="43"/>
+      <c r="O418" s="2"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="O419" s="43"/>
+      <c r="O419" s="2"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="O420" s="43"/>
+      <c r="O420" s="2"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="O421" s="43"/>
+      <c r="O421" s="2"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="O422" s="43"/>
+      <c r="O422" s="2"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="O423" s="43"/>
+      <c r="O423" s="2"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="O424" s="43"/>
+      <c r="O424" s="2"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="O425" s="43"/>
+      <c r="O425" s="2"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="O426" s="43"/>
+      <c r="O426" s="2"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="O427" s="43"/>
+      <c r="O427" s="2"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="O428" s="43"/>
+      <c r="O428" s="2"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="O429" s="43"/>
+      <c r="O429" s="2"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="O430" s="43"/>
+      <c r="O430" s="2"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="O431" s="43"/>
+      <c r="O431" s="2"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="O432" s="43"/>
+      <c r="O432" s="2"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="O433" s="43"/>
+      <c r="O433" s="2"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="O434" s="43"/>
+      <c r="O434" s="2"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="O435" s="43"/>
+      <c r="O435" s="2"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="O436" s="43"/>
+      <c r="O436" s="2"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="O437" s="43"/>
+      <c r="O437" s="2"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="O438" s="43"/>
+      <c r="O438" s="2"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="O439" s="43"/>
+      <c r="O439" s="2"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="O440" s="43"/>
+      <c r="O440" s="2"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="O441" s="43"/>
+      <c r="O441" s="2"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="O442" s="43"/>
+      <c r="O442" s="2"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="O443" s="43"/>
+      <c r="O443" s="2"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="O444" s="43"/>
+      <c r="O444" s="2"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="O445" s="43"/>
+      <c r="O445" s="2"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="O446" s="43"/>
+      <c r="O446" s="2"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="O447" s="43"/>
+      <c r="O447" s="2"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="O448" s="43"/>
+      <c r="O448" s="2"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="O449" s="43"/>
+      <c r="O449" s="2"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="O450" s="43"/>
+      <c r="O450" s="2"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="O451" s="43"/>
+      <c r="O451" s="2"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="O452" s="43"/>
+      <c r="O452" s="2"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="O453" s="43"/>
+      <c r="O453" s="2"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="O454" s="43"/>
+      <c r="O454" s="2"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="O455" s="43"/>
+      <c r="O455" s="2"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="O456" s="43"/>
+      <c r="O456" s="2"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="O457" s="43"/>
+      <c r="O457" s="2"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="O458" s="43"/>
+      <c r="O458" s="2"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="O459" s="43"/>
+      <c r="O459" s="2"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="O460" s="43"/>
+      <c r="O460" s="2"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="O461" s="43"/>
+      <c r="O461" s="2"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="O462" s="43"/>
+      <c r="O462" s="2"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="O463" s="43"/>
+      <c r="O463" s="2"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="O464" s="43"/>
+      <c r="O464" s="2"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="O465" s="43"/>
+      <c r="O465" s="2"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="O466" s="43"/>
+      <c r="O466" s="2"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="O467" s="43"/>
+      <c r="O467" s="2"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="O468" s="43"/>
+      <c r="O468" s="2"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="O469" s="43"/>
+      <c r="O469" s="2"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="O470" s="43"/>
+      <c r="O470" s="2"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="O471" s="43"/>
+      <c r="O471" s="2"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="O472" s="43"/>
+      <c r="O472" s="2"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="O473" s="43"/>
+      <c r="O473" s="2"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="O474" s="43"/>
+      <c r="O474" s="2"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="O475" s="43"/>
+      <c r="O475" s="2"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="O476" s="43"/>
+      <c r="O476" s="2"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="O477" s="43"/>
+      <c r="O477" s="2"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="O478" s="43"/>
+      <c r="O478" s="2"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="O479" s="43"/>
+      <c r="O479" s="2"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="O480" s="43"/>
+      <c r="O480" s="2"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="O481" s="43"/>
+      <c r="O481" s="2"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="O482" s="43"/>
+      <c r="O482" s="2"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="O483" s="43"/>
+      <c r="O483" s="2"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="O484" s="43"/>
+      <c r="O484" s="2"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="O485" s="43"/>
+      <c r="O485" s="2"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="O486" s="43"/>
+      <c r="O486" s="2"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="O487" s="43"/>
+      <c r="O487" s="2"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="O488" s="43"/>
+      <c r="O488" s="2"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="O489" s="43"/>
+      <c r="O489" s="2"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="O490" s="43"/>
+      <c r="O490" s="2"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="O491" s="43"/>
+      <c r="O491" s="2"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="O492" s="43"/>
+      <c r="O492" s="2"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="O493" s="43"/>
+      <c r="O493" s="2"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="O494" s="43"/>
+      <c r="O494" s="2"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="O495" s="43"/>
+      <c r="O495" s="2"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="O496" s="43"/>
+      <c r="O496" s="2"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="O497" s="43"/>
+      <c r="O497" s="2"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="O498" s="43"/>
+      <c r="O498" s="2"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="O499" s="43"/>
+      <c r="O499" s="2"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="O500" s="43"/>
+      <c r="O500" s="2"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="O501" s="43"/>
+      <c r="O501" s="2"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="O502" s="43"/>
+      <c r="O502" s="2"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="O503" s="43"/>
+      <c r="O503" s="2"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="O504" s="43"/>
+      <c r="O504" s="2"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="O505" s="43"/>
+      <c r="O505" s="2"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="O506" s="43"/>
+      <c r="O506" s="2"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="O507" s="43"/>
+      <c r="O507" s="2"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="O508" s="43"/>
+      <c r="O508" s="2"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="O509" s="43"/>
+      <c r="O509" s="2"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="O510" s="43"/>
+      <c r="O510" s="2"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="O511" s="43"/>
+      <c r="O511" s="2"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="O512" s="43"/>
+      <c r="O512" s="2"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="O513" s="43"/>
+      <c r="O513" s="2"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="O514" s="43"/>
+      <c r="O514" s="2"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="O515" s="43"/>
+      <c r="O515" s="2"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="O516" s="43"/>
+      <c r="O516" s="2"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="O517" s="43"/>
+      <c r="O517" s="2"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="O518" s="43"/>
+      <c r="O518" s="2"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="O519" s="43"/>
+      <c r="O519" s="2"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="O520" s="43"/>
+      <c r="O520" s="2"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="O521" s="43"/>
+      <c r="O521" s="2"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="O522" s="43"/>
+      <c r="O522" s="2"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="O523" s="43"/>
+      <c r="O523" s="2"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="O524" s="43"/>
+      <c r="O524" s="2"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="O525" s="43"/>
+      <c r="O525" s="2"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="O526" s="43"/>
+      <c r="O526" s="2"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="O527" s="43"/>
+      <c r="O527" s="2"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="O528" s="43"/>
+      <c r="O528" s="2"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="O529" s="43"/>
+      <c r="O529" s="2"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="O530" s="43"/>
+      <c r="O530" s="2"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="O531" s="43"/>
+      <c r="O531" s="2"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="O532" s="43"/>
+      <c r="O532" s="2"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="O533" s="43"/>
+      <c r="O533" s="2"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="O534" s="43"/>
+      <c r="O534" s="2"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="O535" s="43"/>
+      <c r="O535" s="2"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="O536" s="43"/>
+      <c r="O536" s="2"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="O537" s="43"/>
+      <c r="O537" s="2"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="O538" s="43"/>
+      <c r="O538" s="2"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="O539" s="43"/>
+      <c r="O539" s="2"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="O540" s="43"/>
+      <c r="O540" s="2"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="O541" s="43"/>
+      <c r="O541" s="2"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="O542" s="43"/>
+      <c r="O542" s="2"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="O543" s="43"/>
+      <c r="O543" s="2"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="O544" s="43"/>
+      <c r="O544" s="2"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="O545" s="43"/>
+      <c r="O545" s="2"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="O546" s="43"/>
+      <c r="O546" s="2"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="O547" s="43"/>
+      <c r="O547" s="2"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="O548" s="43"/>
+      <c r="O548" s="2"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="O549" s="43"/>
+      <c r="O549" s="2"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="O550" s="43"/>
+      <c r="O550" s="2"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="O551" s="43"/>
+      <c r="O551" s="2"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="O552" s="43"/>
+      <c r="O552" s="2"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="O553" s="43"/>
+      <c r="O553" s="2"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="O554" s="43"/>
+      <c r="O554" s="2"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="O555" s="43"/>
+      <c r="O555" s="2"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="O556" s="43"/>
+      <c r="O556" s="2"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="O557" s="43"/>
+      <c r="O557" s="2"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="O558" s="43"/>
+      <c r="O558" s="2"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="O559" s="43"/>
+      <c r="O559" s="2"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="O560" s="43"/>
+      <c r="O560" s="2"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="O561" s="43"/>
+      <c r="O561" s="2"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="O562" s="43"/>
+      <c r="O562" s="2"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="O563" s="43"/>
+      <c r="O563" s="2"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="O564" s="43"/>
+      <c r="O564" s="2"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="O565" s="43"/>
+      <c r="O565" s="2"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="O566" s="43"/>
+      <c r="O566" s="2"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="O567" s="43"/>
+      <c r="O567" s="2"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="O568" s="43"/>
+      <c r="O568" s="2"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="O569" s="43"/>
+      <c r="O569" s="2"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="O570" s="43"/>
+      <c r="O570" s="2"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="O571" s="43"/>
+      <c r="O571" s="2"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="O572" s="43"/>
+      <c r="O572" s="2"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="O573" s="43"/>
+      <c r="O573" s="2"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="O574" s="43"/>
+      <c r="O574" s="2"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="O575" s="43"/>
+      <c r="O575" s="2"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="O576" s="43"/>
+      <c r="O576" s="2"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="O577" s="43"/>
+      <c r="O577" s="2"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="O578" s="43"/>
+      <c r="O578" s="2"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="O579" s="43"/>
+      <c r="O579" s="2"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="O580" s="43"/>
+      <c r="O580" s="2"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="O581" s="43"/>
+      <c r="O581" s="2"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="O582" s="43"/>
+      <c r="O582" s="2"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="O583" s="43"/>
+      <c r="O583" s="2"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="O584" s="43"/>
+      <c r="O584" s="2"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="O585" s="43"/>
+      <c r="O585" s="2"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="O586" s="43"/>
+      <c r="O586" s="2"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="O587" s="43"/>
+      <c r="O587" s="2"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="O588" s="43"/>
+      <c r="O588" s="2"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="O589" s="43"/>
+      <c r="O589" s="2"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="O590" s="43"/>
+      <c r="O590" s="2"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="O591" s="43"/>
+      <c r="O591" s="2"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="O592" s="43"/>
+      <c r="O592" s="2"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="O593" s="43"/>
+      <c r="O593" s="2"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="O594" s="43"/>
+      <c r="O594" s="2"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="O595" s="43"/>
+      <c r="O595" s="2"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="O596" s="43"/>
+      <c r="O596" s="2"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="O597" s="43"/>
+      <c r="O597" s="2"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="O598" s="43"/>
+      <c r="O598" s="2"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="O599" s="43"/>
+      <c r="O599" s="2"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="O600" s="43"/>
+      <c r="O600" s="2"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="O601" s="43"/>
+      <c r="O601" s="2"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="O602" s="43"/>
+      <c r="O602" s="2"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="O603" s="43"/>
+      <c r="O603" s="2"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="O604" s="43"/>
+      <c r="O604" s="2"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="O605" s="43"/>
+      <c r="O605" s="2"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="O606" s="43"/>
+      <c r="O606" s="2"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="O607" s="43"/>
+      <c r="O607" s="2"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="O608" s="43"/>
+      <c r="O608" s="2"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="O609" s="43"/>
+      <c r="O609" s="2"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="O610" s="43"/>
+      <c r="O610" s="2"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="O611" s="43"/>
+      <c r="O611" s="2"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="O612" s="43"/>
+      <c r="O612" s="2"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="O613" s="43"/>
+      <c r="O613" s="2"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="O614" s="43"/>
+      <c r="O614" s="2"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="O615" s="43"/>
+      <c r="O615" s="2"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="O616" s="43"/>
+      <c r="O616" s="2"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="O617" s="43"/>
+      <c r="O617" s="2"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="O618" s="43"/>
+      <c r="O618" s="2"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="O619" s="43"/>
+      <c r="O619" s="2"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="O620" s="43"/>
+      <c r="O620" s="2"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="O621" s="43"/>
+      <c r="O621" s="2"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="O622" s="43"/>
+      <c r="O622" s="2"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="O623" s="43"/>
+      <c r="O623" s="2"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="O624" s="43"/>
+      <c r="O624" s="2"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="O625" s="43"/>
+      <c r="O625" s="2"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="O626" s="43"/>
+      <c r="O626" s="2"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="O627" s="43"/>
+      <c r="O627" s="2"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="O628" s="43"/>
+      <c r="O628" s="2"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="O629" s="43"/>
+      <c r="O629" s="2"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="O630" s="43"/>
+      <c r="O630" s="2"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="O631" s="43"/>
+      <c r="O631" s="2"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="O632" s="43"/>
+      <c r="O632" s="2"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="O633" s="43"/>
+      <c r="O633" s="2"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="O634" s="43"/>
+      <c r="O634" s="2"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="O635" s="43"/>
+      <c r="O635" s="2"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="O636" s="43"/>
+      <c r="O636" s="2"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="O637" s="43"/>
+      <c r="O637" s="2"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="O638" s="43"/>
+      <c r="O638" s="2"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="O639" s="43"/>
+      <c r="O639" s="2"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="O640" s="43"/>
+      <c r="O640" s="2"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="O641" s="43"/>
+      <c r="O641" s="2"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="O642" s="43"/>
+      <c r="O642" s="2"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="O643" s="43"/>
+      <c r="O643" s="2"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="O644" s="43"/>
+      <c r="O644" s="2"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="O645" s="43"/>
+      <c r="O645" s="2"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="O646" s="43"/>
+      <c r="O646" s="2"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="O647" s="43"/>
+      <c r="O647" s="2"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="O648" s="43"/>
+      <c r="O648" s="2"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="O649" s="43"/>
+      <c r="O649" s="2"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="O650" s="43"/>
+      <c r="O650" s="2"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="O651" s="43"/>
+      <c r="O651" s="2"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="O652" s="43"/>
+      <c r="O652" s="2"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="O653" s="43"/>
+      <c r="O653" s="2"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="O654" s="43"/>
+      <c r="O654" s="2"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="O655" s="43"/>
+      <c r="O655" s="2"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="O656" s="43"/>
+      <c r="O656" s="2"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="O657" s="43"/>
+      <c r="O657" s="2"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="O658" s="43"/>
+      <c r="O658" s="2"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="O659" s="43"/>
+      <c r="O659" s="2"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="O660" s="43"/>
+      <c r="O660" s="2"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="O661" s="43"/>
+      <c r="O661" s="2"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="O662" s="43"/>
+      <c r="O662" s="2"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="O663" s="43"/>
+      <c r="O663" s="2"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="O664" s="43"/>
+      <c r="O664" s="2"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="O665" s="43"/>
+      <c r="O665" s="2"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="O666" s="43"/>
+      <c r="O666" s="2"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="O667" s="43"/>
+      <c r="O667" s="2"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="O668" s="43"/>
+      <c r="O668" s="2"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="O669" s="43"/>
+      <c r="O669" s="2"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="O670" s="43"/>
+      <c r="O670" s="2"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="O671" s="43"/>
+      <c r="O671" s="2"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="O672" s="43"/>
+      <c r="O672" s="2"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="O673" s="43"/>
+      <c r="O673" s="2"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="O674" s="43"/>
+      <c r="O674" s="2"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="O675" s="43"/>
+      <c r="O675" s="2"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="O676" s="43"/>
+      <c r="O676" s="2"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="O677" s="43"/>
+      <c r="O677" s="2"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="O678" s="43"/>
+      <c r="O678" s="2"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="O679" s="43"/>
+      <c r="O679" s="2"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="O680" s="43"/>
+      <c r="O680" s="2"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="O681" s="43"/>
+      <c r="O681" s="2"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="O682" s="43"/>
+      <c r="O682" s="2"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="O683" s="43"/>
+      <c r="O683" s="2"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="O684" s="43"/>
+      <c r="O684" s="2"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="O685" s="43"/>
+      <c r="O685" s="2"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="O686" s="43"/>
+      <c r="O686" s="2"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="O687" s="43"/>
+      <c r="O687" s="2"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="O688" s="43"/>
+      <c r="O688" s="2"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="O689" s="43"/>
+      <c r="O689" s="2"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="O690" s="43"/>
+      <c r="O690" s="2"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="O691" s="43"/>
+      <c r="O691" s="2"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="O692" s="43"/>
+      <c r="O692" s="2"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="O693" s="43"/>
+      <c r="O693" s="2"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="O694" s="43"/>
+      <c r="O694" s="2"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="O695" s="43"/>
+      <c r="O695" s="2"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="O696" s="43"/>
+      <c r="O696" s="2"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="O697" s="43"/>
+      <c r="O697" s="2"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="O698" s="43"/>
+      <c r="O698" s="2"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="O699" s="43"/>
+      <c r="O699" s="2"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="O700" s="43"/>
+      <c r="O700" s="2"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="O701" s="43"/>
+      <c r="O701" s="2"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="O702" s="43"/>
+      <c r="O702" s="2"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="O703" s="43"/>
+      <c r="O703" s="2"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="O704" s="43"/>
+      <c r="O704" s="2"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="O705" s="43"/>
+      <c r="O705" s="2"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="O706" s="43"/>
+      <c r="O706" s="2"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="O707" s="43"/>
+      <c r="O707" s="2"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="O708" s="43"/>
+      <c r="O708" s="2"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="O709" s="43"/>
+      <c r="O709" s="2"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="O710" s="43"/>
+      <c r="O710" s="2"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="O711" s="43"/>
+      <c r="O711" s="2"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="O712" s="43"/>
+      <c r="O712" s="2"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="O713" s="43"/>
+      <c r="O713" s="2"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="O714" s="43"/>
+      <c r="O714" s="2"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="O715" s="43"/>
+      <c r="O715" s="2"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="O716" s="43"/>
+      <c r="O716" s="2"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="O717" s="43"/>
+      <c r="O717" s="2"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="O718" s="43"/>
+      <c r="O718" s="2"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="O719" s="43"/>
+      <c r="O719" s="2"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="O720" s="43"/>
+      <c r="O720" s="2"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="O721" s="43"/>
+      <c r="O721" s="2"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="O722" s="43"/>
+      <c r="O722" s="2"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="O723" s="43"/>
+      <c r="O723" s="2"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="O724" s="43"/>
+      <c r="O724" s="2"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="O725" s="43"/>
+      <c r="O725" s="2"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="O726" s="43"/>
+      <c r="O726" s="2"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="O727" s="43"/>
+      <c r="O727" s="2"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="O728" s="43"/>
+      <c r="O728" s="2"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="O729" s="43"/>
+      <c r="O729" s="2"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="O730" s="43"/>
+      <c r="O730" s="2"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="O731" s="43"/>
+      <c r="O731" s="2"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="O732" s="43"/>
+      <c r="O732" s="2"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="O733" s="43"/>
+      <c r="O733" s="2"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="O734" s="43"/>
+      <c r="O734" s="2"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="O735" s="43"/>
+      <c r="O735" s="2"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="O736" s="43"/>
+      <c r="O736" s="2"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="O737" s="43"/>
+      <c r="O737" s="2"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="O738" s="43"/>
+      <c r="O738" s="2"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="O739" s="43"/>
+      <c r="O739" s="2"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="O740" s="43"/>
+      <c r="O740" s="2"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="O741" s="43"/>
+      <c r="O741" s="2"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="O742" s="43"/>
+      <c r="O742" s="2"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="O743" s="43"/>
+      <c r="O743" s="2"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="O744" s="43"/>
+      <c r="O744" s="2"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="O745" s="43"/>
+      <c r="O745" s="2"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="O746" s="43"/>
+      <c r="O746" s="2"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="O747" s="43"/>
+      <c r="O747" s="2"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="O748" s="43"/>
+      <c r="O748" s="2"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="O749" s="43"/>
+      <c r="O749" s="2"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="O750" s="43"/>
+      <c r="O750" s="2"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="O751" s="43"/>
+      <c r="O751" s="2"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="O752" s="43"/>
+      <c r="O752" s="2"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="O753" s="43"/>
+      <c r="O753" s="2"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="O754" s="43"/>
+      <c r="O754" s="2"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="O755" s="43"/>
+      <c r="O755" s="2"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="O756" s="43"/>
+      <c r="O756" s="2"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="O757" s="43"/>
+      <c r="O757" s="2"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="O758" s="43"/>
+      <c r="O758" s="2"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="O759" s="43"/>
+      <c r="O759" s="2"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="O760" s="43"/>
+      <c r="O760" s="2"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="O761" s="43"/>
+      <c r="O761" s="2"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="O762" s="43"/>
+      <c r="O762" s="2"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="O763" s="43"/>
+      <c r="O763" s="2"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="O764" s="43"/>
+      <c r="O764" s="2"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="O765" s="43"/>
+      <c r="O765" s="2"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="O766" s="43"/>
+      <c r="O766" s="2"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="O767" s="43"/>
+      <c r="O767" s="2"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="O768" s="43"/>
+      <c r="O768" s="2"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="O769" s="43"/>
+      <c r="O769" s="2"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="O770" s="43"/>
+      <c r="O770" s="2"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="O771" s="43"/>
+      <c r="O771" s="2"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="O772" s="43"/>
+      <c r="O772" s="2"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="O773" s="43"/>
+      <c r="O773" s="2"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="O774" s="43"/>
+      <c r="O774" s="2"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="O775" s="43"/>
+      <c r="O775" s="2"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="O776" s="43"/>
+      <c r="O776" s="2"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="O777" s="43"/>
+      <c r="O777" s="2"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="O778" s="43"/>
+      <c r="O778" s="2"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="O779" s="43"/>
+      <c r="O779" s="2"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="O780" s="43"/>
+      <c r="O780" s="2"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="O781" s="43"/>
+      <c r="O781" s="2"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="O782" s="43"/>
+      <c r="O782" s="2"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="O783" s="43"/>
+      <c r="O783" s="2"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="O784" s="43"/>
+      <c r="O784" s="2"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="O785" s="43"/>
+      <c r="O785" s="2"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="O786" s="43"/>
+      <c r="O786" s="2"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="O787" s="43"/>
+      <c r="O787" s="2"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="O788" s="43"/>
+      <c r="O788" s="2"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="O789" s="43"/>
+      <c r="O789" s="2"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="O790" s="43"/>
+      <c r="O790" s="2"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="O791" s="43"/>
+      <c r="O791" s="2"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="O792" s="43"/>
+      <c r="O792" s="2"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="O793" s="43"/>
+      <c r="O793" s="2"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="O794" s="43"/>
+      <c r="O794" s="2"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="O795" s="43"/>
+      <c r="O795" s="2"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="O796" s="43"/>
+      <c r="O796" s="2"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="O797" s="43"/>
+      <c r="O797" s="2"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="O798" s="43"/>
+      <c r="O798" s="2"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="O799" s="43"/>
+      <c r="O799" s="2"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="O800" s="43"/>
+      <c r="O800" s="2"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="O801" s="43"/>
+      <c r="O801" s="2"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="O802" s="43"/>
+      <c r="O802" s="2"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="O803" s="43"/>
+      <c r="O803" s="2"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="O804" s="43"/>
+      <c r="O804" s="2"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="O805" s="43"/>
+      <c r="O805" s="2"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="O806" s="43"/>
+      <c r="O806" s="2"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="O807" s="43"/>
+      <c r="O807" s="2"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="O808" s="43"/>
+      <c r="O808" s="2"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="O809" s="43"/>
+      <c r="O809" s="2"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="O810" s="43"/>
+      <c r="O810" s="2"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="O811" s="43"/>
+      <c r="O811" s="2"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="O812" s="43"/>
+      <c r="O812" s="2"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="O813" s="43"/>
+      <c r="O813" s="2"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="O814" s="43"/>
+      <c r="O814" s="2"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="O815" s="43"/>
+      <c r="O815" s="2"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="O816" s="43"/>
+      <c r="O816" s="2"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="O817" s="43"/>
+      <c r="O817" s="2"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="O818" s="43"/>
+      <c r="O818" s="2"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="O819" s="43"/>
+      <c r="O819" s="2"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="O820" s="43"/>
+      <c r="O820" s="2"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="O821" s="43"/>
+      <c r="O821" s="2"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="O822" s="43"/>
+      <c r="O822" s="2"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="O823" s="43"/>
+      <c r="O823" s="2"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="O824" s="43"/>
+      <c r="O824" s="2"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="O825" s="43"/>
+      <c r="O825" s="2"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="O826" s="43"/>
+      <c r="O826" s="2"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="O827" s="43"/>
+      <c r="O827" s="2"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="O828" s="43"/>
+      <c r="O828" s="2"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="O829" s="43"/>
+      <c r="O829" s="2"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="O830" s="43"/>
+      <c r="O830" s="2"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="O831" s="43"/>
+      <c r="O831" s="2"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="O832" s="43"/>
+      <c r="O832" s="2"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="O833" s="43"/>
+      <c r="O833" s="2"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="O834" s="43"/>
+      <c r="O834" s="2"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="O835" s="43"/>
+      <c r="O835" s="2"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="O836" s="43"/>
+      <c r="O836" s="2"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="O837" s="43"/>
+      <c r="O837" s="2"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="O838" s="43"/>
+      <c r="O838" s="2"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="O839" s="43"/>
+      <c r="O839" s="2"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="O840" s="43"/>
+      <c r="O840" s="2"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="O841" s="43"/>
+      <c r="O841" s="2"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="O842" s="43"/>
+      <c r="O842" s="2"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="O843" s="43"/>
+      <c r="O843" s="2"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="O844" s="43"/>
+      <c r="O844" s="2"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="O845" s="43"/>
+      <c r="O845" s="2"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="O846" s="43"/>
+      <c r="O846" s="2"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="O847" s="43"/>
+      <c r="O847" s="2"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="O848" s="43"/>
+      <c r="O848" s="2"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="O849" s="43"/>
+      <c r="O849" s="2"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="O850" s="43"/>
+      <c r="O850" s="2"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="O851" s="43"/>
+      <c r="O851" s="2"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="O852" s="43"/>
+      <c r="O852" s="2"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="O853" s="43"/>
+      <c r="O853" s="2"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="O854" s="43"/>
+      <c r="O854" s="2"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="O855" s="43"/>
+      <c r="O855" s="2"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="O856" s="43"/>
+      <c r="O856" s="2"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="O857" s="43"/>
+      <c r="O857" s="2"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="O858" s="43"/>
+      <c r="O858" s="2"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="O859" s="43"/>
+      <c r="O859" s="2"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="O860" s="43"/>
+      <c r="O860" s="2"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="O861" s="43"/>
+      <c r="O861" s="2"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="O862" s="43"/>
+      <c r="O862" s="2"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="O863" s="43"/>
+      <c r="O863" s="2"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="O864" s="43"/>
+      <c r="O864" s="2"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="O865" s="43"/>
+      <c r="O865" s="2"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="O866" s="43"/>
+      <c r="O866" s="2"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="O867" s="43"/>
+      <c r="O867" s="2"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="O868" s="43"/>
+      <c r="O868" s="2"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="O869" s="43"/>
+      <c r="O869" s="2"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="O870" s="43"/>
+      <c r="O870" s="2"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="O871" s="43"/>
+      <c r="O871" s="2"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="O872" s="43"/>
+      <c r="O872" s="2"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="O873" s="43"/>
+      <c r="O873" s="2"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="O874" s="43"/>
+      <c r="O874" s="2"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="O875" s="43"/>
+      <c r="O875" s="2"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="O876" s="43"/>
+      <c r="O876" s="2"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="O877" s="43"/>
+      <c r="O877" s="2"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="O878" s="43"/>
+      <c r="O878" s="2"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="O879" s="43"/>
+      <c r="O879" s="2"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="O880" s="43"/>
+      <c r="O880" s="2"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="O881" s="43"/>
+      <c r="O881" s="2"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="O882" s="43"/>
+      <c r="O882" s="2"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="O883" s="43"/>
+      <c r="O883" s="2"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="O884" s="43"/>
+      <c r="O884" s="2"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="O885" s="43"/>
+      <c r="O885" s="2"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="O886" s="43"/>
+      <c r="O886" s="2"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="O887" s="43"/>
+      <c r="O887" s="2"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="O888" s="43"/>
+      <c r="O888" s="2"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="O889" s="43"/>
+      <c r="O889" s="2"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="O890" s="43"/>
+      <c r="O890" s="2"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="O891" s="43"/>
+      <c r="O891" s="2"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="O892" s="43"/>
+      <c r="O892" s="2"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="O893" s="43"/>
+      <c r="O893" s="2"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="O894" s="43"/>
+      <c r="O894" s="2"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="O895" s="43"/>
+      <c r="O895" s="2"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="O896" s="43"/>
+      <c r="O896" s="2"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="O897" s="43"/>
+      <c r="O897" s="2"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="O898" s="43"/>
+      <c r="O898" s="2"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="O899" s="43"/>
+      <c r="O899" s="2"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="O900" s="43"/>
+      <c r="O900" s="2"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="O901" s="43"/>
+      <c r="O901" s="2"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="O902" s="43"/>
+      <c r="O902" s="2"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="O903" s="43"/>
+      <c r="O903" s="2"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="O904" s="43"/>
+      <c r="O904" s="2"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="O905" s="43"/>
+      <c r="O905" s="2"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="O906" s="43"/>
+      <c r="O906" s="2"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="O907" s="43"/>
+      <c r="O907" s="2"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="O908" s="43"/>
+      <c r="O908" s="2"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="O909" s="43"/>
+      <c r="O909" s="2"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="O910" s="43"/>
+      <c r="O910" s="2"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="O911" s="43"/>
+      <c r="O911" s="2"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="O912" s="43"/>
+      <c r="O912" s="2"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="O913" s="43"/>
+      <c r="O913" s="2"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="O914" s="43"/>
+      <c r="O914" s="2"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="O915" s="43"/>
+      <c r="O915" s="2"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="O916" s="43"/>
+      <c r="O916" s="2"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="O917" s="43"/>
+      <c r="O917" s="2"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="O918" s="43"/>
+      <c r="O918" s="2"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="O919" s="43"/>
+      <c r="O919" s="2"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="O920" s="43"/>
+      <c r="O920" s="2"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="O921" s="43"/>
+      <c r="O921" s="2"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="O922" s="43"/>
+      <c r="O922" s="2"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="O923" s="43"/>
+      <c r="O923" s="2"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="O924" s="43"/>
+      <c r="O924" s="2"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="O925" s="43"/>
+      <c r="O925" s="2"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="O926" s="43"/>
+      <c r="O926" s="2"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="O927" s="43"/>
+      <c r="O927" s="2"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="O928" s="43"/>
+      <c r="O928" s="2"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="O929" s="43"/>
+      <c r="O929" s="2"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="O930" s="43"/>
+      <c r="O930" s="2"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="O931" s="43"/>
+      <c r="O931" s="2"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="O932" s="43"/>
+      <c r="O932" s="2"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="O933" s="43"/>
+      <c r="O933" s="2"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="O934" s="43"/>
+      <c r="O934" s="2"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="O935" s="43"/>
+      <c r="O935" s="2"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="O936" s="43"/>
+      <c r="O936" s="2"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="O937" s="43"/>
+      <c r="O937" s="2"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="O938" s="43"/>
+      <c r="O938" s="2"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="O939" s="43"/>
+      <c r="O939" s="2"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="O940" s="43"/>
+      <c r="O940" s="2"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="O941" s="43"/>
+      <c r="O941" s="2"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="O942" s="43"/>
+      <c r="O942" s="2"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="O943" s="43"/>
+      <c r="O943" s="2"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="O944" s="43"/>
+      <c r="O944" s="2"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="O945" s="43"/>
+      <c r="O945" s="2"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="O946" s="43"/>
+      <c r="O946" s="2"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="O947" s="43"/>
+      <c r="O947" s="2"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="O948" s="43"/>
+      <c r="O948" s="2"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="O949" s="43"/>
+      <c r="O949" s="2"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="O950" s="43"/>
+      <c r="O950" s="2"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="O951" s="43"/>
+      <c r="O951" s="2"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="O952" s="43"/>
+      <c r="O952" s="2"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="O953" s="43"/>
+      <c r="O953" s="2"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="O954" s="43"/>
+      <c r="O954" s="2"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="O955" s="43"/>
+      <c r="O955" s="2"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="O956" s="43"/>
+      <c r="O956" s="2"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="O957" s="43"/>
+      <c r="O957" s="2"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="O958" s="43"/>
+      <c r="O958" s="2"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="O959" s="43"/>
+      <c r="O959" s="2"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="O960" s="43"/>
+      <c r="O960" s="2"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="O961" s="43"/>
+      <c r="O961" s="2"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="O962" s="43"/>
+      <c r="O962" s="2"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="O963" s="43"/>
+      <c r="O963" s="2"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="O964" s="43"/>
+      <c r="O964" s="2"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="O965" s="43"/>
+      <c r="O965" s="2"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="O966" s="43"/>
+      <c r="O966" s="2"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="O967" s="43"/>
+      <c r="O967" s="2"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="O968" s="43"/>
+      <c r="O968" s="2"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="O969" s="43"/>
+      <c r="O969" s="2"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="O970" s="43"/>
+      <c r="O970" s="2"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="O971" s="43"/>
+      <c r="O971" s="2"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="O972" s="43"/>
+      <c r="O972" s="2"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="O973" s="43"/>
+      <c r="O973" s="2"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="O974" s="43"/>
+      <c r="O974" s="2"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="O975" s="43"/>
+      <c r="O975" s="2"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="O976" s="43"/>
+      <c r="O976" s="2"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="O977" s="43"/>
+      <c r="O977" s="2"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="O978" s="43"/>
+      <c r="O978" s="2"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="O979" s="43"/>
+      <c r="O979" s="2"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="O980" s="43"/>
+      <c r="O980" s="2"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="O981" s="43"/>
+      <c r="O981" s="2"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="O982" s="43"/>
+      <c r="O982" s="2"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="O983" s="43"/>
+      <c r="O983" s="2"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="O984" s="43"/>
+      <c r="O984" s="2"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="O985" s="43"/>
+      <c r="O985" s="2"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="O986" s="43"/>
+      <c r="O986" s="2"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="O987" s="43"/>
+      <c r="O987" s="2"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="O988" s="43"/>
+      <c r="O988" s="2"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="O989" s="43"/>
+      <c r="O989" s="2"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="O990" s="43"/>
+      <c r="O990" s="2"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="O991" s="43"/>
+      <c r="O991" s="2"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="O992" s="43"/>
+      <c r="O992" s="2"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="O993" s="43"/>
+      <c r="O993" s="2"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="O994" s="43"/>
+      <c r="O994" s="2"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="O995" s="43"/>
+      <c r="O995" s="2"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="O996" s="43"/>
+      <c r="O996" s="2"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="O997" s="43"/>
+      <c r="O997" s="2"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="O998" s="43"/>
+      <c r="O998" s="2"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="O999" s="43"/>
+      <c r="O999" s="2"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="O1000" s="43"/>
+      <c r="O1000" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
